--- a/漢字（かんじ）/ji.xlsx
+++ b/漢字（かんじ）/ji.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="じ" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="123">
   <si>
     <t>仮名</t>
   </si>
@@ -73,6 +73,18 @@
 一時｜いちじ</t>
   </si>
   <si>
+    <t>甚</t>
+  </si>
+  <si>
+    <t>甚大｜じんだい</t>
+  </si>
+  <si>
+    <t>寺</t>
+  </si>
+  <si>
+    <t>寺院｜じいん</t>
+  </si>
+  <si>
     <t>じゅん</t>
   </si>
   <si>
@@ -85,10 +97,12 @@
 下旬｜げじゅん</t>
   </si>
   <si>
-    <t>寺</t>
-  </si>
-  <si>
-    <t>寺院｜じいん</t>
+    <t>持</t>
+  </si>
+  <si>
+    <t>持続｜じぞく
+維持｜いじ
+支持｜しじ</t>
   </si>
   <si>
     <t>準</t>
@@ -99,12 +113,10 @@
 標準偏差｜ひょうじゅんへんさ</t>
   </si>
   <si>
-    <t>持</t>
-  </si>
-  <si>
-    <t>持続｜じぞく
-維持｜いじ
-支持｜しじ</t>
+    <t>辞</t>
+  </si>
+  <si>
+    <t>辞表｜じじょう</t>
   </si>
   <si>
     <t>順</t>
@@ -114,28 +126,16 @@
 順調｜じゅんちょう</t>
   </si>
   <si>
-    <t>辞</t>
-  </si>
-  <si>
-    <t>辞表｜じじょう</t>
+    <t>字</t>
+  </si>
+  <si>
+    <t>漢字｜かんじ</t>
   </si>
   <si>
     <t>盾</t>
   </si>
   <si>
     <t>矛盾｜むじゅん</t>
-  </si>
-  <si>
-    <t>字</t>
-  </si>
-  <si>
-    <t>漢字｜かんじ</t>
-  </si>
-  <si>
-    <t>循</t>
-  </si>
-  <si>
-    <t>循環｜じゅんかん</t>
   </si>
   <si>
     <t>地</t>
@@ -146,10 +146,10 @@
 無地｜むじ</t>
   </si>
   <si>
-    <t>遵</t>
-  </si>
-  <si>
-    <t>遵守｜じゅんしゅ</t>
+    <t>循</t>
+  </si>
+  <si>
+    <t>循環｜じゅんかん</t>
   </si>
   <si>
     <t>事</t>
@@ -164,6 +164,19 @@
 工事｜こうじ</t>
   </si>
   <si>
+    <t>遵</t>
+  </si>
+  <si>
+    <t>遵守｜じゅんしゅ</t>
+  </si>
+  <si>
+    <t>似</t>
+  </si>
+  <si>
+    <t>類似｜るいじ
+相似｜ろうじ</t>
+  </si>
+  <si>
     <t>純</t>
   </si>
   <si>
@@ -171,11 +184,11 @@
 清純｜せいじゅん</t>
   </si>
   <si>
-    <t>似</t>
-  </si>
-  <si>
-    <t>類似｜るいじ
-相似｜ろうじ</t>
+    <t>示</t>
+  </si>
+  <si>
+    <t>表示｜ひょうじ
+告示｜こくじ</t>
   </si>
   <si>
     <t>巡</t>
@@ -184,19 +197,6 @@
     <t>巡回｜じゅんかい
 巡回訪問｜じゅんかいほうもん
 巡回監督｜じゅんかいかんとく</t>
-  </si>
-  <si>
-    <t>示</t>
-  </si>
-  <si>
-    <t>表示｜ひょうじ
-告示｜こくじ</t>
-  </si>
-  <si>
-    <t>潤</t>
-  </si>
-  <si>
-    <t>湿潤｜しつじゅん</t>
   </si>
   <si>
     <t>じょ</t>
@@ -211,6 +211,19 @@
 次女｜じじょ</t>
   </si>
   <si>
+    <t>潤</t>
+  </si>
+  <si>
+    <t>湿潤｜しつじゅん</t>
+  </si>
+  <si>
+    <t>序</t>
+  </si>
+  <si>
+    <t>序列｜じょれつ
+年功序列｜ねんこうじょれつ</t>
+  </si>
+  <si>
     <t>じゅつ</t>
   </si>
   <si>
@@ -222,11 +235,13 @@
 手術｜てじゅつ</t>
   </si>
   <si>
-    <t>序</t>
-  </si>
-  <si>
-    <t>序列｜じょれつ
-年功序列｜ねんこうじょれつ</t>
+    <t>除</t>
+  </si>
+  <si>
+    <t>解除｜かいじょ
+除法｜じょほう
+削除｜さくじょ
+免除｜めんじょ</t>
   </si>
   <si>
     <t>述</t>
@@ -262,13 +277,13 @@
     </r>
   </si>
   <si>
-    <t>除</t>
-  </si>
-  <si>
-    <t>解除｜かいじょ
-除法｜じょほう
-削除｜さくじょ
-免除｜めんじょ</t>
+    <t>助</t>
+  </si>
+  <si>
+    <t>補助｜ほじょ
+補助金｜ほじょきん
+援助｜えんじょ
+助手｜じょしゅ</t>
   </si>
   <si>
     <t>じつ</t>
@@ -292,13 +307,10 @@
 実需品｜じつじゅひん</t>
   </si>
   <si>
-    <t>助</t>
-  </si>
-  <si>
-    <t>補助｜ほじょ
-補助金｜ほじょきん
-援助｜えんじょ
-助手｜じょしゅ</t>
+    <t>所</t>
+  </si>
+  <si>
+    <t>停留所｜ていりゅじょ</t>
   </si>
   <si>
     <t>日</t>
@@ -309,10 +321,14 @@
 平日｜へいじつ</t>
   </si>
   <si>
-    <t>所</t>
-  </si>
-  <si>
-    <t>停留所｜ていりゅじょ</t>
+    <t>じょう</t>
+  </si>
+  <si>
+    <t>状</t>
+  </si>
+  <si>
+    <t>環状線｜かんじょうせん
+状態｜じょうたい</t>
   </si>
   <si>
     <t>じょく</t>
@@ -325,14 +341,11 @@
 侮辱｜ぶじょく</t>
   </si>
   <si>
-    <t>じょう</t>
-  </si>
-  <si>
-    <t>状</t>
-  </si>
-  <si>
-    <t>環状線｜かんじょうせん
-状態｜じょうたい</t>
+    <t>場</t>
+  </si>
+  <si>
+    <t>会場｜かいじょう
+競技場｜きょうぎじょう</t>
   </si>
   <si>
     <t>じゅく</t>
@@ -345,11 +358,11 @@
 学習塾｜がくしゅうじゅく</t>
   </si>
   <si>
-    <t>場</t>
-  </si>
-  <si>
-    <t>会場｜かいじょう
-競技場｜きょうぎじょう</t>
+    <t>条</t>
+  </si>
+  <si>
+    <t>条例｜じょうれい
+条件｜じょうけん</t>
   </si>
   <si>
     <t>じゃ</t>
@@ -360,13 +373,6 @@
   <si>
     <t>邪魔｜じゃま
 邪悪｜じゃあく</t>
-  </si>
-  <si>
-    <t>条</t>
-  </si>
-  <si>
-    <t>条例｜じょうれい
-条件｜じょうけん</t>
   </si>
   <si>
     <t>蒸</t>
@@ -527,7 +533,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -540,13 +546,6 @@
       <color theme="1"/>
       <name val="Yu Gothic"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1002,148 +1001,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1522,7 +1521,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="72" spans="1:7">
+    <row r="3" ht="36" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1533,27 +1532,27 @@
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" ht="54" spans="1:7">
+    </row>
+    <row r="4" ht="72" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>16</v>
@@ -1573,7 +1572,7 @@
         <v>19</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>20</v>
@@ -1582,7 +1581,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" ht="36" spans="1:7">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
@@ -1593,7 +1592,7 @@
         <v>23</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>24</v>
@@ -1613,12 +1612,12 @@
         <v>27</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="2" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1633,7 +1632,7 @@
         <v>31</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>32</v>
@@ -1653,16 +1652,16 @@
         <v>35</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="10" ht="54" spans="1:7">
+    <row r="10" ht="36" spans="1:7">
       <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
@@ -1673,7 +1672,7 @@
         <v>39</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>40</v>
@@ -1682,7 +1681,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" ht="36" spans="1:7">
+    <row r="11" ht="54" spans="1:7">
       <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
@@ -1693,12 +1692,12 @@
         <v>43</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="2" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1713,27 +1712,27 @@
         <v>48</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" ht="36" spans="1:7">
+    </row>
+    <row r="13" ht="54" spans="1:7">
       <c r="A13" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="E13" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>54</v>
@@ -1753,27 +1752,27 @@
         <v>57</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" ht="72" spans="1:7">
+    </row>
+    <row r="15" ht="234" spans="1:7">
       <c r="A15" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="E15" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>63</v>
@@ -1782,7 +1781,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" ht="36" spans="1:7">
+    <row r="16" ht="54" spans="1:7">
       <c r="A16" s="1" t="s">
         <v>46</v>
       </c>
@@ -1793,262 +1792,271 @@
         <v>66</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="17" ht="36.6" customHeight="1" spans="1:7">
       <c r="A17" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C17" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="E17" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="18" ht="36" spans="1:7">
       <c r="A18" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="E18" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="G18" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="19" ht="36" spans="1:7">
       <c r="A19" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="E19" s="1" t="s">
         <v>82</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" ht="126" spans="1:7">
       <c r="A21" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" ht="72" spans="1:7">
       <c r="A22" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" ht="54" spans="1:7">
       <c r="A24" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" ht="144" spans="1:7">
       <c r="A25" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" ht="54" spans="1:7">
       <c r="A26" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" ht="54" spans="1:7">
       <c r="A30" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" ht="144" spans="1:7">
       <c r="A32" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" ht="36" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" ht="54" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36" ht="36" spans="1:3">
       <c r="A36" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37" ht="36" spans="1:3">
       <c r="A37" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/漢字（かんじ）/ji.xlsx
+++ b/漢字（かんじ）/ji.xlsx
@@ -413,7 +413,8 @@
   <si>
     <t>情報｜じょうほう
 感情｜かんじょう
-愛情｜あいじょう</t>
+愛情｜あいじょう
+強情｜ごうじょう</t>
   </si>
   <si>
     <t>常</t>
@@ -1905,7 +1906,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="24" ht="54" spans="1:7">
+    <row r="24" ht="72" spans="1:7">
       <c r="A24" s="1" t="s">
         <v>69</v>
       </c>

--- a/漢字（かんじ）/ji.xlsx
+++ b/漢字（かんじ）/ji.xlsx
@@ -464,7 +464,9 @@
   <si>
     <t>需要｜じゅよう
 実需｜じつじゅ
-実需品｜じつじゅひん</t>
+実需品｜じつじゅひん
+必需｜ひつじゅ
+必需品｜ひつじゅひん</t>
   </si>
   <si>
     <t>授</t>
@@ -1972,7 +1974,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="30" ht="54" spans="1:7">
+    <row r="30" ht="90" spans="1:7">
       <c r="A30" s="1" t="s">
         <v>103</v>
       </c>
